--- a/ksoft_old/docs/stock/Bestand_Decorative_Paper_Set_up_details.xlsx
+++ b/ksoft_old/docs/stock/Bestand_Decorative_Paper_Set_up_details.xlsx
@@ -58466,13 +58466,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5F957B6-0C1F-4EF3-A6C1-1972AA10729D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6AEC411-3F69-49C6-A5C6-2E64EFB7F99A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D497F969-FBF5-4437-9A48-556D6C7137DB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A83D564-7FDC-4E13-B3B6-E1FCFAEDC1C9}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4FB5DC94-7630-472E-BADD-D29D229ACDF6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CC8D478-AFC5-496D-AB9E-BBF0FA45DE73}"/>
 </file>
--- a/ksoft_old/docs/stock/Bestand_Decorative_Paper_Set_up_details.xlsx
+++ b/ksoft_old/docs/stock/Bestand_Decorative_Paper_Set_up_details.xlsx
@@ -58466,13 +58466,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6AEC411-3F69-49C6-A5C6-2E64EFB7F99A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0794AC4-A0F0-40F5-8B8C-C698AE49C362}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A83D564-7FDC-4E13-B3B6-E1FCFAEDC1C9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82BC2540-05F7-42C2-8588-932D33F19FFB}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CC8D478-AFC5-496D-AB9E-BBF0FA45DE73}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DAF9A4B0-4C7D-4D76-B07A-3BBBD5A1F0FF}"/>
 </file>
--- a/ksoft_old/docs/stock/Bestand_Decorative_Paper_Set_up_details.xlsx
+++ b/ksoft_old/docs/stock/Bestand_Decorative_Paper_Set_up_details.xlsx
@@ -58466,13 +58466,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0794AC4-A0F0-40F5-8B8C-C698AE49C362}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5F957B6-0C1F-4EF3-A6C1-1972AA10729D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82BC2540-05F7-42C2-8588-932D33F19FFB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D497F969-FBF5-4437-9A48-556D6C7137DB}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DAF9A4B0-4C7D-4D76-B07A-3BBBD5A1F0FF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4FB5DC94-7630-472E-BADD-D29D229ACDF6}"/>
 </file>